--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ReportRevealManage001.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ReportRevealManage001.xlsx
@@ -1,20 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="300" windowWidth="12705" windowHeight="2910"/>
+    <workbookView windowWidth="18530" windowHeight="7130"/>
   </bookViews>
   <sheets>
     <sheet name="报表披露信息" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+  <si>
+    <t>披露状态</t>
+  </si>
+  <si>
+    <t>产品代码</t>
+  </si>
+  <si>
+    <t>产品名称</t>
+  </si>
+  <si>
+    <t>报表名称</t>
+  </si>
+  <si>
+    <t>报告期</t>
+  </si>
+  <si>
+    <t>披露截止日</t>
+  </si>
+  <si>
+    <t>报表类别</t>
+  </si>
   <si>
     <t>文件名称</t>
   </si>
@@ -37,81 +58,201 @@
     <t>披露方式</t>
   </si>
   <si>
-    <t>附件</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>披露人</t>
   </si>
   <si>
-    <t>披露状态</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>产品代码</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>产品名称</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>报表名称</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>报告期</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>披露截止日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>报表类别</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>附件</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="7">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="#,##0.00_ "/>
     <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
     <numFmt numFmtId="178" formatCode="0.00000_ "/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -120,18 +261,204 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -141,66 +468,352 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="42" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 10" xfId="1"/>
+    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
+    <cellStyle name="输入" xfId="3" builtinId="20"/>
+    <cellStyle name="货币" xfId="4" builtinId="4"/>
+    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
+    <cellStyle name="差" xfId="7" builtinId="27"/>
+    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
+    <cellStyle name="超链接" xfId="10" builtinId="8"/>
+    <cellStyle name="百分比" xfId="11" builtinId="5"/>
+    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
+    <cellStyle name="注释" xfId="13" builtinId="10"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
+    <cellStyle name="标题" xfId="17" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
+    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
+    <cellStyle name="输出" xfId="24" builtinId="21"/>
+    <cellStyle name="计算" xfId="25" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
+    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
+    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
+    <cellStyle name="汇总" xfId="30" builtinId="25"/>
+    <cellStyle name="好" xfId="31" builtinId="26"/>
+    <cellStyle name="适中" xfId="32" builtinId="28"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
+    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
+    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
+    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
+    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="常规 10" xfId="47"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="48" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="49" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -249,7 +862,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -284,7 +897,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -487,79 +1100,82 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O22"/>
-  <sheetFormatPr defaultColWidth="13.625" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:P22"/>
+  <sheetFormatPr defaultColWidth="13.6272727272727" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="3" width="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.25" style="1" customWidth="1"/>
-    <col min="6" max="6" width="15.875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="13" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="22.375" style="2" customWidth="1"/>
-    <col min="9" max="9" width="9" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13" bestFit="1" customWidth="1"/>
+    <col min="1" max="3" width="9" customWidth="1"/>
+    <col min="4" max="4" width="9" style="2" customWidth="1"/>
+    <col min="5" max="5" width="20.2545454545455" style="2" customWidth="1"/>
+    <col min="6" max="6" width="15.8727272727273" style="2" customWidth="1"/>
+    <col min="7" max="7" width="13" style="3" customWidth="1"/>
+    <col min="8" max="8" width="22.3727272727273" style="3" customWidth="1"/>
+    <col min="9" max="9" width="9" customWidth="1"/>
+    <col min="10" max="10" width="13" customWidth="1"/>
     <col min="13" max="13" width="18.5" customWidth="1"/>
-    <col min="14" max="14" width="11.75" customWidth="1"/>
-    <col min="15" max="15" width="30" customWidth="1"/>
-    <col min="16" max="16" width="14.25" customWidth="1"/>
-    <col min="20" max="20" width="14.75" customWidth="1"/>
-    <col min="21" max="21" width="14.5" customWidth="1"/>
+    <col min="14" max="15" width="11.7545454545455" customWidth="1"/>
+    <col min="16" max="16" width="30" customWidth="1"/>
+    <col min="17" max="17" width="14.2545454545455" customWidth="1"/>
+    <col min="21" max="21" width="14.7545454545455" customWidth="1"/>
+    <col min="22" max="22" width="14.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="3" t="s">
+    <row r="1" ht="20.1" customHeight="1" spans="1:16">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="J1" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="K1" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="L1" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="M1" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="N1" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="O1" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="H1" s="5" t="s">
-        <v>0</v>
+      <c r="P1" s="10" t="s">
+        <v>15</v>
       </c>
-      <c r="I1" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="J1" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="L1" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="M1" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="N1" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="O1" s="6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="2" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:16">
       <c r="A2" s="7"/>
       <c r="B2" s="7"/>
       <c r="C2" s="7"/>
@@ -568,15 +1184,16 @@
       <c r="F2" s="9"/>
       <c r="G2" s="9"/>
       <c r="H2" s="9"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
-      <c r="N2" s="10"/>
-      <c r="O2" s="10"/>
-    </row>
-    <row r="3" spans="1:15" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="I2" s="11"/>
+      <c r="J2" s="11"/>
+      <c r="K2" s="11"/>
+      <c r="L2" s="11"/>
+      <c r="M2" s="11"/>
+      <c r="N2" s="11"/>
+      <c r="O2" s="11"/>
+      <c r="P2" s="11"/>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:16">
       <c r="A3" s="7"/>
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
@@ -585,15 +1202,16 @@
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
       <c r="H3" s="9"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="10"/>
-      <c r="K3" s="10"/>
-      <c r="L3" s="10"/>
-      <c r="M3" s="10"/>
-      <c r="N3" s="10"/>
-      <c r="O3" s="10"/>
-    </row>
-    <row r="4" spans="1:15" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="I3" s="11"/>
+      <c r="J3" s="11"/>
+      <c r="K3" s="11"/>
+      <c r="L3" s="11"/>
+      <c r="M3" s="11"/>
+      <c r="N3" s="11"/>
+      <c r="O3" s="11"/>
+      <c r="P3" s="11"/>
+    </row>
+    <row r="4" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:16">
       <c r="A4" s="7"/>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -602,15 +1220,16 @@
       <c r="F4" s="9"/>
       <c r="G4" s="9"/>
       <c r="H4" s="9"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10"/>
-      <c r="K4" s="10"/>
-      <c r="L4" s="10"/>
-      <c r="M4" s="10"/>
-      <c r="N4" s="10"/>
-      <c r="O4" s="10"/>
-    </row>
-    <row r="5" spans="1:15" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="I4" s="11"/>
+      <c r="J4" s="11"/>
+      <c r="K4" s="11"/>
+      <c r="L4" s="11"/>
+      <c r="M4" s="11"/>
+      <c r="N4" s="11"/>
+      <c r="O4" s="11"/>
+      <c r="P4" s="11"/>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:16">
       <c r="A5" s="7"/>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -619,15 +1238,16 @@
       <c r="F5" s="9"/>
       <c r="G5" s="9"/>
       <c r="H5" s="9"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="10"/>
-      <c r="K5" s="10"/>
-      <c r="L5" s="10"/>
-      <c r="M5" s="10"/>
-      <c r="N5" s="10"/>
-      <c r="O5" s="10"/>
-    </row>
-    <row r="6" spans="1:15" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="11"/>
+      <c r="L5" s="11"/>
+      <c r="M5" s="11"/>
+      <c r="N5" s="11"/>
+      <c r="O5" s="11"/>
+      <c r="P5" s="11"/>
+    </row>
+    <row r="6" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:16">
       <c r="A6" s="7"/>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
@@ -636,15 +1256,16 @@
       <c r="F6" s="9"/>
       <c r="G6" s="9"/>
       <c r="H6" s="9"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="10"/>
-      <c r="K6" s="10"/>
-      <c r="L6" s="10"/>
-      <c r="M6" s="10"/>
-      <c r="N6" s="10"/>
-      <c r="O6" s="10"/>
-    </row>
-    <row r="7" spans="1:15" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
+      <c r="N6" s="11"/>
+      <c r="O6" s="11"/>
+      <c r="P6" s="11"/>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:16">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
@@ -653,15 +1274,16 @@
       <c r="F7" s="9"/>
       <c r="G7" s="9"/>
       <c r="H7" s="9"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="10"/>
-      <c r="L7" s="10"/>
-      <c r="M7" s="10"/>
-      <c r="N7" s="10"/>
-      <c r="O7" s="10"/>
-    </row>
-    <row r="8" spans="1:15" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="I7" s="11"/>
+      <c r="J7" s="11"/>
+      <c r="K7" s="11"/>
+      <c r="L7" s="11"/>
+      <c r="M7" s="11"/>
+      <c r="N7" s="11"/>
+      <c r="O7" s="11"/>
+      <c r="P7" s="11"/>
+    </row>
+    <row r="8" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:16">
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
@@ -670,15 +1292,16 @@
       <c r="F8" s="9"/>
       <c r="G8" s="9"/>
       <c r="H8" s="9"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="10"/>
-      <c r="K8" s="10"/>
-      <c r="L8" s="10"/>
-      <c r="M8" s="10"/>
-      <c r="N8" s="10"/>
-      <c r="O8" s="10"/>
-    </row>
-    <row r="9" spans="1:15" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="I8" s="11"/>
+      <c r="J8" s="11"/>
+      <c r="K8" s="11"/>
+      <c r="L8" s="11"/>
+      <c r="M8" s="11"/>
+      <c r="N8" s="11"/>
+      <c r="O8" s="11"/>
+      <c r="P8" s="11"/>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:16">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
@@ -687,15 +1310,16 @@
       <c r="F9" s="9"/>
       <c r="G9" s="9"/>
       <c r="H9" s="9"/>
-      <c r="I9" s="10"/>
-      <c r="J9" s="10"/>
-      <c r="K9" s="10"/>
-      <c r="L9" s="10"/>
-      <c r="M9" s="10"/>
-      <c r="N9" s="10"/>
-      <c r="O9" s="10"/>
-    </row>
-    <row r="10" spans="1:15" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="I9" s="11"/>
+      <c r="J9" s="11"/>
+      <c r="K9" s="11"/>
+      <c r="L9" s="11"/>
+      <c r="M9" s="11"/>
+      <c r="N9" s="11"/>
+      <c r="O9" s="11"/>
+      <c r="P9" s="11"/>
+    </row>
+    <row r="10" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:16">
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
@@ -704,15 +1328,16 @@
       <c r="F10" s="9"/>
       <c r="G10" s="9"/>
       <c r="H10" s="9"/>
-      <c r="I10" s="10"/>
-      <c r="J10" s="10"/>
-      <c r="K10" s="10"/>
-      <c r="L10" s="10"/>
-      <c r="M10" s="10"/>
-      <c r="N10" s="10"/>
-      <c r="O10" s="10"/>
-    </row>
-    <row r="11" spans="1:15" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="I10" s="11"/>
+      <c r="J10" s="11"/>
+      <c r="K10" s="11"/>
+      <c r="L10" s="11"/>
+      <c r="M10" s="11"/>
+      <c r="N10" s="11"/>
+      <c r="O10" s="11"/>
+      <c r="P10" s="11"/>
+    </row>
+    <row r="11" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:16">
       <c r="A11" s="7"/>
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
@@ -721,15 +1346,16 @@
       <c r="F11" s="9"/>
       <c r="G11" s="9"/>
       <c r="H11" s="9"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="10"/>
-      <c r="K11" s="10"/>
-      <c r="L11" s="10"/>
-      <c r="M11" s="10"/>
-      <c r="N11" s="10"/>
-      <c r="O11" s="10"/>
-    </row>
-    <row r="12" spans="1:15" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="I11" s="11"/>
+      <c r="J11" s="11"/>
+      <c r="K11" s="11"/>
+      <c r="L11" s="11"/>
+      <c r="M11" s="11"/>
+      <c r="N11" s="11"/>
+      <c r="O11" s="11"/>
+      <c r="P11" s="11"/>
+    </row>
+    <row r="12" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:16">
       <c r="A12" s="7"/>
       <c r="B12" s="7"/>
       <c r="C12" s="7"/>
@@ -738,15 +1364,16 @@
       <c r="F12" s="9"/>
       <c r="G12" s="9"/>
       <c r="H12" s="9"/>
-      <c r="I12" s="10"/>
-      <c r="J12" s="10"/>
-      <c r="K12" s="10"/>
-      <c r="L12" s="10"/>
-      <c r="M12" s="10"/>
-      <c r="N12" s="10"/>
-      <c r="O12" s="10"/>
-    </row>
-    <row r="13" spans="1:15" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="I12" s="11"/>
+      <c r="J12" s="11"/>
+      <c r="K12" s="11"/>
+      <c r="L12" s="11"/>
+      <c r="M12" s="11"/>
+      <c r="N12" s="11"/>
+      <c r="O12" s="11"/>
+      <c r="P12" s="11"/>
+    </row>
+    <row r="13" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:16">
       <c r="A13" s="7"/>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
@@ -755,15 +1382,16 @@
       <c r="F13" s="9"/>
       <c r="G13" s="9"/>
       <c r="H13" s="9"/>
-      <c r="I13" s="10"/>
-      <c r="J13" s="10"/>
-      <c r="K13" s="10"/>
-      <c r="L13" s="10"/>
-      <c r="M13" s="10"/>
-      <c r="N13" s="10"/>
-      <c r="O13" s="10"/>
-    </row>
-    <row r="14" spans="1:15" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="I13" s="11"/>
+      <c r="J13" s="11"/>
+      <c r="K13" s="11"/>
+      <c r="L13" s="11"/>
+      <c r="M13" s="11"/>
+      <c r="N13" s="11"/>
+      <c r="O13" s="11"/>
+      <c r="P13" s="11"/>
+    </row>
+    <row r="14" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:16">
       <c r="A14" s="7"/>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
@@ -772,15 +1400,16 @@
       <c r="F14" s="9"/>
       <c r="G14" s="9"/>
       <c r="H14" s="9"/>
-      <c r="I14" s="10"/>
-      <c r="J14" s="10"/>
-      <c r="K14" s="10"/>
-      <c r="L14" s="10"/>
-      <c r="M14" s="10"/>
-      <c r="N14" s="10"/>
-      <c r="O14" s="10"/>
-    </row>
-    <row r="15" spans="1:15" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="I14" s="11"/>
+      <c r="J14" s="11"/>
+      <c r="K14" s="11"/>
+      <c r="L14" s="11"/>
+      <c r="M14" s="11"/>
+      <c r="N14" s="11"/>
+      <c r="O14" s="11"/>
+      <c r="P14" s="11"/>
+    </row>
+    <row r="15" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:16">
       <c r="A15" s="7"/>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
@@ -789,15 +1418,16 @@
       <c r="F15" s="9"/>
       <c r="G15" s="9"/>
       <c r="H15" s="9"/>
-      <c r="I15" s="10"/>
-      <c r="J15" s="10"/>
-      <c r="K15" s="10"/>
-      <c r="L15" s="10"/>
-      <c r="M15" s="10"/>
-      <c r="N15" s="10"/>
-      <c r="O15" s="10"/>
-    </row>
-    <row r="16" spans="1:15" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="I15" s="11"/>
+      <c r="J15" s="11"/>
+      <c r="K15" s="11"/>
+      <c r="L15" s="11"/>
+      <c r="M15" s="11"/>
+      <c r="N15" s="11"/>
+      <c r="O15" s="11"/>
+      <c r="P15" s="11"/>
+    </row>
+    <row r="16" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:16">
       <c r="A16" s="7"/>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
@@ -806,15 +1436,16 @@
       <c r="F16" s="9"/>
       <c r="G16" s="9"/>
       <c r="H16" s="9"/>
-      <c r="I16" s="10"/>
-      <c r="J16" s="10"/>
-      <c r="K16" s="10"/>
-      <c r="L16" s="10"/>
-      <c r="M16" s="10"/>
-      <c r="N16" s="10"/>
-      <c r="O16" s="10"/>
-    </row>
-    <row r="17" spans="1:15" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="I16" s="11"/>
+      <c r="J16" s="11"/>
+      <c r="K16" s="11"/>
+      <c r="L16" s="11"/>
+      <c r="M16" s="11"/>
+      <c r="N16" s="11"/>
+      <c r="O16" s="11"/>
+      <c r="P16" s="11"/>
+    </row>
+    <row r="17" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:16">
       <c r="A17" s="7"/>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
@@ -823,15 +1454,16 @@
       <c r="F17" s="9"/>
       <c r="G17" s="9"/>
       <c r="H17" s="9"/>
-      <c r="I17" s="10"/>
-      <c r="J17" s="10"/>
-      <c r="K17" s="10"/>
-      <c r="L17" s="10"/>
-      <c r="M17" s="10"/>
-      <c r="N17" s="10"/>
-      <c r="O17" s="10"/>
-    </row>
-    <row r="18" spans="1:15" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="I17" s="11"/>
+      <c r="J17" s="11"/>
+      <c r="K17" s="11"/>
+      <c r="L17" s="11"/>
+      <c r="M17" s="11"/>
+      <c r="N17" s="11"/>
+      <c r="O17" s="11"/>
+      <c r="P17" s="11"/>
+    </row>
+    <row r="18" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:16">
       <c r="A18" s="7"/>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
@@ -840,15 +1472,16 @@
       <c r="F18" s="9"/>
       <c r="G18" s="9"/>
       <c r="H18" s="9"/>
-      <c r="I18" s="10"/>
-      <c r="J18" s="10"/>
-      <c r="K18" s="10"/>
-      <c r="L18" s="10"/>
-      <c r="M18" s="10"/>
-      <c r="N18" s="10"/>
-      <c r="O18" s="10"/>
-    </row>
-    <row r="19" spans="1:15" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="I18" s="11"/>
+      <c r="J18" s="11"/>
+      <c r="K18" s="11"/>
+      <c r="L18" s="11"/>
+      <c r="M18" s="11"/>
+      <c r="N18" s="11"/>
+      <c r="O18" s="11"/>
+      <c r="P18" s="11"/>
+    </row>
+    <row r="19" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:16">
       <c r="A19" s="7"/>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
@@ -857,15 +1490,16 @@
       <c r="F19" s="9"/>
       <c r="G19" s="9"/>
       <c r="H19" s="9"/>
-      <c r="I19" s="10"/>
-      <c r="J19" s="10"/>
-      <c r="K19" s="10"/>
-      <c r="L19" s="10"/>
-      <c r="M19" s="10"/>
-      <c r="N19" s="10"/>
-      <c r="O19" s="10"/>
-    </row>
-    <row r="20" spans="1:15" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="I19" s="11"/>
+      <c r="J19" s="11"/>
+      <c r="K19" s="11"/>
+      <c r="L19" s="11"/>
+      <c r="M19" s="11"/>
+      <c r="N19" s="11"/>
+      <c r="O19" s="11"/>
+      <c r="P19" s="11"/>
+    </row>
+    <row r="20" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:16">
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
@@ -874,15 +1508,16 @@
       <c r="F20" s="9"/>
       <c r="G20" s="9"/>
       <c r="H20" s="9"/>
-      <c r="I20" s="10"/>
-      <c r="J20" s="10"/>
-      <c r="K20" s="10"/>
-      <c r="L20" s="10"/>
-      <c r="M20" s="10"/>
-      <c r="N20" s="10"/>
-      <c r="O20" s="10"/>
-    </row>
-    <row r="21" spans="1:15" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="I20" s="11"/>
+      <c r="J20" s="11"/>
+      <c r="K20" s="11"/>
+      <c r="L20" s="11"/>
+      <c r="M20" s="11"/>
+      <c r="N20" s="11"/>
+      <c r="O20" s="11"/>
+      <c r="P20" s="11"/>
+    </row>
+    <row r="21" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:16">
       <c r="A21" s="7"/>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
@@ -891,15 +1526,16 @@
       <c r="F21" s="9"/>
       <c r="G21" s="9"/>
       <c r="H21" s="9"/>
-      <c r="I21" s="10"/>
-      <c r="J21" s="10"/>
-      <c r="K21" s="10"/>
-      <c r="L21" s="10"/>
-      <c r="M21" s="10"/>
-      <c r="N21" s="10"/>
-      <c r="O21" s="10"/>
-    </row>
-    <row r="22" spans="1:15" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="I21" s="11"/>
+      <c r="J21" s="11"/>
+      <c r="K21" s="11"/>
+      <c r="L21" s="11"/>
+      <c r="M21" s="11"/>
+      <c r="N21" s="11"/>
+      <c r="O21" s="11"/>
+      <c r="P21" s="11"/>
+    </row>
+    <row r="22" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:16">
       <c r="A22" s="7"/>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
@@ -908,17 +1544,18 @@
       <c r="F22" s="9"/>
       <c r="G22" s="9"/>
       <c r="H22" s="9"/>
-      <c r="I22" s="10"/>
-      <c r="J22" s="10"/>
-      <c r="K22" s="10"/>
-      <c r="L22" s="10"/>
-      <c r="M22" s="10"/>
-      <c r="N22" s="10"/>
-      <c r="O22" s="10"/>
+      <c r="I22" s="11"/>
+      <c r="J22" s="11"/>
+      <c r="K22" s="11"/>
+      <c r="L22" s="11"/>
+      <c r="M22" s="11"/>
+      <c r="N22" s="11"/>
+      <c r="O22" s="11"/>
+      <c r="P22" s="11"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ReportRevealManage001.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ReportRevealManage001.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25726"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JoyinWork\NYXP\tams\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Git\NY\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{650BA2B6-881C-4932-ACA4-F7F7E387F10D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="30930" windowHeight="16890"/>
   </bookViews>
   <sheets>
     <sheet name="报表披露信息" sheetId="1" r:id="rId1"/>
@@ -28,9 +27,6 @@
     <t>产品代码</t>
   </si>
   <si>
-    <t>产品名称</t>
-  </si>
-  <si>
     <t>报表名称</t>
   </si>
   <si>
@@ -74,13 +70,17 @@
   </si>
   <si>
     <t>托管复核人</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>产品全称</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="3">
     <numFmt numFmtId="176" formatCode="#,##0.00_ "/>
     <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
@@ -208,7 +208,7 @@
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 10" xfId="1" xr:uid="{00000000-0005-0000-0000-00002F000000}"/>
+    <cellStyle name="常规 10" xfId="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -509,85 +509,85 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Q22"/>
-  <sheetFormatPr defaultColWidth="13.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="13.625" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
-    <col min="2" max="2" width="15.44140625" customWidth="1"/>
-    <col min="3" max="3" width="14.33203125" customWidth="1"/>
+    <col min="2" max="2" width="15.5" customWidth="1"/>
+    <col min="3" max="3" width="14.375" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
     <col min="5" max="5" width="9" style="2" customWidth="1"/>
-    <col min="6" max="6" width="20.21875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="15.88671875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="20.25" style="2" customWidth="1"/>
+    <col min="7" max="7" width="15.875" style="2" customWidth="1"/>
     <col min="8" max="8" width="13" style="3" customWidth="1"/>
-    <col min="9" max="9" width="22.33203125" style="3" customWidth="1"/>
-    <col min="10" max="10" width="15.5546875" customWidth="1"/>
-    <col min="11" max="11" width="19.33203125" customWidth="1"/>
-    <col min="13" max="13" width="20.5546875" customWidth="1"/>
-    <col min="14" max="14" width="11.77734375" customWidth="1"/>
-    <col min="15" max="15" width="19.33203125" customWidth="1"/>
-    <col min="16" max="16" width="11.77734375" customWidth="1"/>
+    <col min="9" max="9" width="22.375" style="3" customWidth="1"/>
+    <col min="10" max="10" width="15.5" customWidth="1"/>
+    <col min="11" max="11" width="19.375" customWidth="1"/>
+    <col min="13" max="13" width="20.5" customWidth="1"/>
+    <col min="14" max="14" width="11.75" customWidth="1"/>
+    <col min="15" max="15" width="19.375" customWidth="1"/>
+    <col min="16" max="16" width="11.75" customWidth="1"/>
     <col min="17" max="17" width="30" customWidth="1"/>
-    <col min="18" max="18" width="14.21875" customWidth="1"/>
-    <col min="22" max="22" width="14.77734375" customWidth="1"/>
-    <col min="23" max="23" width="14.44140625" customWidth="1"/>
+    <col min="18" max="18" width="14.25" customWidth="1"/>
+    <col min="22" max="22" width="14.75" customWidth="1"/>
+    <col min="23" max="23" width="14.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="G1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="H1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="I1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="J1" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="K1" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="L1" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="10" t="s">
-        <v>10</v>
-      </c>
       <c r="M1" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="N1" s="12" t="s">
+      <c r="O1" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="O1" s="12" t="s">
+      <c r="P1" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="P1" s="12" t="s">
-        <v>16</v>
-      </c>
       <c r="Q1" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="7"/>
       <c r="B2" s="11"/>
       <c r="C2" s="7"/>
@@ -606,7 +606,7 @@
       <c r="P2" s="11"/>
       <c r="Q2" s="11"/>
     </row>
-    <row r="3" spans="1:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="7"/>
       <c r="B3" s="11"/>
       <c r="C3" s="7"/>
@@ -625,7 +625,7 @@
       <c r="P3" s="11"/>
       <c r="Q3" s="11"/>
     </row>
-    <row r="4" spans="1:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="7"/>
       <c r="B4" s="11"/>
       <c r="C4" s="7"/>
@@ -644,7 +644,7 @@
       <c r="P4" s="11"/>
       <c r="Q4" s="11"/>
     </row>
-    <row r="5" spans="1:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="7"/>
       <c r="B5" s="11"/>
       <c r="C5" s="7"/>
@@ -663,7 +663,7 @@
       <c r="P5" s="11"/>
       <c r="Q5" s="11"/>
     </row>
-    <row r="6" spans="1:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="7"/>
       <c r="B6" s="11"/>
       <c r="C6" s="7"/>
@@ -682,7 +682,7 @@
       <c r="P6" s="11"/>
       <c r="Q6" s="11"/>
     </row>
-    <row r="7" spans="1:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="7"/>
       <c r="B7" s="11"/>
       <c r="C7" s="7"/>
@@ -701,7 +701,7 @@
       <c r="P7" s="11"/>
       <c r="Q7" s="11"/>
     </row>
-    <row r="8" spans="1:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="7"/>
       <c r="B8" s="11"/>
       <c r="C8" s="7"/>
@@ -720,7 +720,7 @@
       <c r="P8" s="11"/>
       <c r="Q8" s="11"/>
     </row>
-    <row r="9" spans="1:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="7"/>
       <c r="B9" s="11"/>
       <c r="C9" s="7"/>
@@ -739,7 +739,7 @@
       <c r="P9" s="11"/>
       <c r="Q9" s="11"/>
     </row>
-    <row r="10" spans="1:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="7"/>
       <c r="B10" s="11"/>
       <c r="C10" s="7"/>
@@ -758,7 +758,7 @@
       <c r="P10" s="11"/>
       <c r="Q10" s="11"/>
     </row>
-    <row r="11" spans="1:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="7"/>
       <c r="B11" s="11"/>
       <c r="C11" s="7"/>
@@ -777,7 +777,7 @@
       <c r="P11" s="11"/>
       <c r="Q11" s="11"/>
     </row>
-    <row r="12" spans="1:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="7"/>
       <c r="B12" s="11"/>
       <c r="C12" s="7"/>
@@ -796,7 +796,7 @@
       <c r="P12" s="11"/>
       <c r="Q12" s="11"/>
     </row>
-    <row r="13" spans="1:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="7"/>
       <c r="B13" s="11"/>
       <c r="C13" s="7"/>
@@ -815,7 +815,7 @@
       <c r="P13" s="11"/>
       <c r="Q13" s="11"/>
     </row>
-    <row r="14" spans="1:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="7"/>
       <c r="B14" s="11"/>
       <c r="C14" s="7"/>
@@ -834,7 +834,7 @@
       <c r="P14" s="11"/>
       <c r="Q14" s="11"/>
     </row>
-    <row r="15" spans="1:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="7"/>
       <c r="B15" s="11"/>
       <c r="C15" s="7"/>
@@ -853,7 +853,7 @@
       <c r="P15" s="11"/>
       <c r="Q15" s="11"/>
     </row>
-    <row r="16" spans="1:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="7"/>
       <c r="B16" s="11"/>
       <c r="C16" s="7"/>
@@ -872,7 +872,7 @@
       <c r="P16" s="11"/>
       <c r="Q16" s="11"/>
     </row>
-    <row r="17" spans="1:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="7"/>
       <c r="B17" s="11"/>
       <c r="C17" s="7"/>
@@ -891,7 +891,7 @@
       <c r="P17" s="11"/>
       <c r="Q17" s="11"/>
     </row>
-    <row r="18" spans="1:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="7"/>
       <c r="B18" s="11"/>
       <c r="C18" s="7"/>
@@ -910,7 +910,7 @@
       <c r="P18" s="11"/>
       <c r="Q18" s="11"/>
     </row>
-    <row r="19" spans="1:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="7"/>
       <c r="B19" s="11"/>
       <c r="C19" s="7"/>
@@ -929,7 +929,7 @@
       <c r="P19" s="11"/>
       <c r="Q19" s="11"/>
     </row>
-    <row r="20" spans="1:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="7"/>
       <c r="B20" s="11"/>
       <c r="C20" s="7"/>
@@ -948,7 +948,7 @@
       <c r="P20" s="11"/>
       <c r="Q20" s="11"/>
     </row>
-    <row r="21" spans="1:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="7"/>
       <c r="B21" s="11"/>
       <c r="C21" s="7"/>
@@ -967,7 +967,7 @@
       <c r="P21" s="11"/>
       <c r="Q21" s="11"/>
     </row>
-    <row r="22" spans="1:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="7"/>
       <c r="B22" s="11"/>
       <c r="C22" s="7"/>
